--- a/tams-invest-parent/tams-invest-product/src/main/resources/tpl/FinProductBuild.xlsx
+++ b/tams-invest-parent/tams-invest-product/src/main/resources/tpl/FinProductBuild.xlsx
@@ -4,21 +4,17 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13725" windowHeight="2670"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13730" windowHeight="2670"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
-  <si>
-    <t>有效状态</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>组合代码</t>
   </si>
@@ -126,14 +122,6 @@
   </si>
   <si>
     <t>发送状态备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>产品设计系列编号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>产品设计系列名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -487,35 +475,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:AD1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="9.875" customWidth="1"/>
-    <col min="5" max="5" width="9.125" customWidth="1"/>
-    <col min="6" max="6" width="9.5" customWidth="1"/>
-    <col min="9" max="9" width="12.75" customWidth="1"/>
-    <col min="10" max="13" width="13.25" customWidth="1"/>
-    <col min="14" max="16" width="21.75" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.375" customWidth="1"/>
-    <col min="18" max="18" width="16.625" customWidth="1"/>
-    <col min="19" max="19" width="17.875" customWidth="1"/>
-    <col min="29" max="29" width="16.875" customWidth="1"/>
-    <col min="30" max="30" width="17.5" customWidth="1"/>
-    <col min="33" max="33" width="14.75" customWidth="1"/>
+    <col min="1" max="3" width="9.90625" customWidth="1"/>
+    <col min="4" max="4" width="9.08984375" customWidth="1"/>
+    <col min="5" max="5" width="9.453125" customWidth="1"/>
+    <col min="8" max="8" width="12.7265625" customWidth="1"/>
+    <col min="9" max="12" width="13.26953125" customWidth="1"/>
+    <col min="13" max="15" width="21.7265625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="12.36328125" customWidth="1"/>
+    <col min="17" max="17" width="16.6328125" customWidth="1"/>
+    <col min="18" max="18" width="17.90625" customWidth="1"/>
+    <col min="30" max="30" width="14.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
         <v>29</v>
       </c>
       <c r="C1" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="D1" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E1" t="s">
         <v>1</v>
@@ -524,10 +510,10 @@
         <v>2</v>
       </c>
       <c r="G1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" t="s">
         <v>3</v>
-      </c>
-      <c r="H1" t="s">
-        <v>13</v>
       </c>
       <c r="I1" t="s">
         <v>4</v>
@@ -541,7 +527,7 @@
       <c r="L1" t="s">
         <v>7</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="N1" s="1" t="s">
@@ -550,10 +536,10 @@
       <c r="O1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q1" t="s">
+      <c r="P1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>14</v>
       </c>
       <c r="R1" s="1" t="s">
@@ -590,19 +576,10 @@
         <v>25</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF1" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
